--- a/AAII_Financials/Quarterly/WIGBY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/WIGBY_QTR_FIN.xlsx
@@ -2211,10 +2211,10 @@
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>4003700</v>
+        <v>4061600</v>
       </c>
       <c r="E49" s="3">
-        <v>4003700</v>
+        <v>4061600</v>
       </c>
       <c r="F49" s="3">
         <v>1807200</v>
